--- a/balance/levels.xlsx
+++ b/balance/levels.xlsx
@@ -578,7 +578,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="9">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="C6" s="8">
         <v>0</v>
@@ -590,11 +590,11 @@
         <v>2</v>
       </c>
       <c r="B7" s="9">
-        <v>413</v>
-      </c>
-      <c r="C7" s="8" t="e">
-        <f t="shared" ref="C7:C38" si="0">C5+B5</f>
-        <v>#VALUE!</v>
+        <v>150</v>
+      </c>
+      <c r="C7" s="8">
+        <f t="shared" ref="C7:C38" si="0">C6+B6</f>
+        <v>60</v>
       </c>
       <c r="D7" s="7"/>
     </row>
@@ -603,11 +603,11 @@
         <v>3</v>
       </c>
       <c r="B8" s="9">
-        <v>525</v>
+        <v>300</v>
       </c>
       <c r="C8" s="8">
         <f t="shared" si="0"/>
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="D8" s="7"/>
     </row>
@@ -616,11 +616,11 @@
         <v>4</v>
       </c>
       <c r="B9" s="9">
-        <v>638</v>
-      </c>
-      <c r="C9" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>500</v>
+      </c>
+      <c r="C9" s="8">
+        <f t="shared" si="0"/>
+        <v>510</v>
       </c>
       <c r="D9" s="7"/>
     </row>
@@ -633,7 +633,7 @@
       </c>
       <c r="C10" s="8">
         <f t="shared" si="0"/>
-        <v>825</v>
+        <v>1010</v>
       </c>
       <c r="D10" s="7"/>
     </row>
@@ -644,9 +644,9 @@
       <c r="B11" s="9">
         <v>863</v>
       </c>
-      <c r="C11" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+      <c r="C11" s="8">
+        <f t="shared" si="0"/>
+        <v>1760</v>
       </c>
       <c r="D11" s="7"/>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="C12" s="8">
         <f t="shared" si="0"/>
-        <v>1575</v>
+        <v>2623</v>
       </c>
       <c r="D12" s="7"/>
     </row>
@@ -670,9 +670,9 @@
       <c r="B13" s="9">
         <v>1088</v>
       </c>
-      <c r="C13" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+      <c r="C13" s="8">
+        <f t="shared" si="0"/>
+        <v>3598</v>
       </c>
       <c r="D13" s="7"/>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="C14" s="8">
         <f t="shared" si="0"/>
-        <v>2550</v>
+        <v>4686</v>
       </c>
       <c r="D14" s="7"/>
     </row>
@@ -696,9 +696,9 @@
       <c r="B15" s="9">
         <v>1313</v>
       </c>
-      <c r="C15" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+      <c r="C15" s="8">
+        <f t="shared" si="0"/>
+        <v>5886</v>
       </c>
       <c r="D15" s="7"/>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="C16" s="8">
         <f t="shared" si="0"/>
-        <v>3750</v>
+        <v>7199</v>
       </c>
       <c r="D16" s="7"/>
     </row>
@@ -722,9 +722,9 @@
       <c r="B17" s="9">
         <v>1538</v>
       </c>
-      <c r="C17" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+      <c r="C17" s="8">
+        <f t="shared" si="0"/>
+        <v>8624</v>
       </c>
       <c r="D17" s="7"/>
     </row>
@@ -737,7 +737,7 @@
       </c>
       <c r="C18" s="8">
         <f t="shared" si="0"/>
-        <v>5175</v>
+        <v>10162</v>
       </c>
       <c r="D18" s="7"/>
     </row>
@@ -748,9 +748,9 @@
       <c r="B19" s="9">
         <v>1763</v>
       </c>
-      <c r="C19" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+      <c r="C19" s="8">
+        <f t="shared" si="0"/>
+        <v>11812</v>
       </c>
       <c r="D19" s="7"/>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="C20" s="8">
         <f t="shared" si="0"/>
-        <v>6825</v>
+        <v>13575</v>
       </c>
       <c r="D20" s="7"/>
     </row>
@@ -774,9 +774,9 @@
       <c r="B21" s="9">
         <v>1988</v>
       </c>
-      <c r="C21" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+      <c r="C21" s="8">
+        <f t="shared" si="0"/>
+        <v>15450</v>
       </c>
       <c r="D21" s="7"/>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="C22" s="8">
         <f t="shared" si="0"/>
-        <v>8700</v>
+        <v>17438</v>
       </c>
       <c r="D22" s="7"/>
     </row>
@@ -800,9 +800,9 @@
       <c r="B23" s="9">
         <v>2213</v>
       </c>
-      <c r="C23" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+      <c r="C23" s="8">
+        <f t="shared" si="0"/>
+        <v>19538</v>
       </c>
       <c r="D23" s="7"/>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="C24" s="8">
         <f t="shared" si="0"/>
-        <v>10800</v>
+        <v>21751</v>
       </c>
       <c r="D24" s="7"/>
     </row>
@@ -826,9 +826,9 @@
       <c r="B25" s="9">
         <v>2438</v>
       </c>
-      <c r="C25" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+      <c r="C25" s="8">
+        <f t="shared" si="0"/>
+        <v>24076</v>
       </c>
       <c r="D25" s="7"/>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="C26" s="8">
         <f t="shared" si="0"/>
-        <v>13125</v>
+        <v>26514</v>
       </c>
       <c r="D26" s="7"/>
     </row>
@@ -852,9 +852,9 @@
       <c r="B27" s="9">
         <v>2663</v>
       </c>
-      <c r="C27" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+      <c r="C27" s="8">
+        <f t="shared" si="0"/>
+        <v>29064</v>
       </c>
       <c r="D27" s="7"/>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="C28" s="8">
         <f t="shared" si="0"/>
-        <v>15675</v>
+        <v>31727</v>
       </c>
       <c r="D28" s="7"/>
     </row>
@@ -878,9 +878,9 @@
       <c r="B29" s="9">
         <v>2888</v>
       </c>
-      <c r="C29" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+      <c r="C29" s="8">
+        <f t="shared" si="0"/>
+        <v>34502</v>
       </c>
       <c r="D29" s="7"/>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="C30" s="8">
         <f t="shared" si="0"/>
-        <v>18450</v>
+        <v>37390</v>
       </c>
       <c r="D30" s="7"/>
     </row>
@@ -904,9 +904,9 @@
       <c r="B31" s="9">
         <v>3113</v>
       </c>
-      <c r="C31" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+      <c r="C31" s="8">
+        <f t="shared" si="0"/>
+        <v>40390</v>
       </c>
       <c r="D31" s="7"/>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="C32" s="8">
         <f t="shared" si="0"/>
-        <v>21450</v>
+        <v>43503</v>
       </c>
       <c r="D32" s="7"/>
     </row>
@@ -930,9 +930,9 @@
       <c r="B33" s="9">
         <v>3338</v>
       </c>
-      <c r="C33" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+      <c r="C33" s="8">
+        <f t="shared" si="0"/>
+        <v>46728</v>
       </c>
       <c r="D33" s="7"/>
     </row>
@@ -945,7 +945,7 @@
       </c>
       <c r="C34" s="8">
         <f t="shared" si="0"/>
-        <v>24675</v>
+        <v>50066</v>
       </c>
       <c r="D34" s="7"/>
     </row>
@@ -956,9 +956,9 @@
       <c r="B35" s="9">
         <v>3563</v>
       </c>
-      <c r="C35" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+      <c r="C35" s="8">
+        <f t="shared" si="0"/>
+        <v>53516</v>
       </c>
       <c r="D35" s="7"/>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="C36" s="8">
         <f t="shared" si="0"/>
-        <v>28125</v>
+        <v>57079</v>
       </c>
       <c r="D36" s="7"/>
     </row>
@@ -982,9 +982,9 @@
       <c r="B37" s="9">
         <v>3788</v>
       </c>
-      <c r="C37" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+      <c r="C37" s="8">
+        <f t="shared" si="0"/>
+        <v>60754</v>
       </c>
       <c r="D37" s="7"/>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C38" s="8">
         <f t="shared" si="0"/>
-        <v>31800</v>
+        <v>64542</v>
       </c>
       <c r="D38" s="7"/>
     </row>
@@ -1008,9 +1008,9 @@
       <c r="B39" s="9">
         <v>4013</v>
       </c>
-      <c r="C39" s="8" t="e">
-        <f t="shared" ref="C39:C70" si="1">C37+B37</f>
-        <v>#VALUE!</v>
+      <c r="C39" s="8">
+        <f t="shared" ref="C39:C65" si="1">C38+B38</f>
+        <v>68442</v>
       </c>
       <c r="D39" s="7"/>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C40" s="8">
         <f t="shared" si="1"/>
-        <v>35700</v>
+        <v>72455</v>
       </c>
       <c r="D40" s="7"/>
     </row>
@@ -1034,9 +1034,9 @@
       <c r="B41" s="9">
         <v>4238</v>
       </c>
-      <c r="C41" s="8" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+      <c r="C41" s="8">
+        <f t="shared" si="1"/>
+        <v>76580</v>
       </c>
       <c r="D41" s="7"/>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C42" s="8">
         <f t="shared" si="1"/>
-        <v>39825</v>
+        <v>80818</v>
       </c>
       <c r="D42" s="7"/>
     </row>
@@ -1060,9 +1060,9 @@
       <c r="B43" s="9">
         <v>4463</v>
       </c>
-      <c r="C43" s="8" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+      <c r="C43" s="8">
+        <f t="shared" si="1"/>
+        <v>85168</v>
       </c>
       <c r="D43" s="7"/>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C44" s="8">
         <f t="shared" si="1"/>
-        <v>44175</v>
+        <v>89631</v>
       </c>
       <c r="D44" s="7"/>
     </row>
@@ -1086,9 +1086,9 @@
       <c r="B45" s="9">
         <v>4688</v>
       </c>
-      <c r="C45" s="8" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+      <c r="C45" s="8">
+        <f t="shared" si="1"/>
+        <v>94206</v>
       </c>
       <c r="D45" s="7"/>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="C46" s="8">
         <f t="shared" si="1"/>
-        <v>48750</v>
+        <v>98894</v>
       </c>
       <c r="D46" s="7"/>
     </row>
@@ -1112,9 +1112,9 @@
       <c r="B47" s="9">
         <v>4913</v>
       </c>
-      <c r="C47" s="8" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+      <c r="C47" s="8">
+        <f t="shared" si="1"/>
+        <v>103694</v>
       </c>
       <c r="D47" s="7"/>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="C48" s="8">
         <f t="shared" si="1"/>
-        <v>53550</v>
+        <v>108607</v>
       </c>
       <c r="D48" s="7"/>
     </row>
@@ -1138,9 +1138,9 @@
       <c r="B49" s="9">
         <v>5138</v>
       </c>
-      <c r="C49" s="8" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+      <c r="C49" s="8">
+        <f t="shared" si="1"/>
+        <v>113632</v>
       </c>
       <c r="D49" s="7"/>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C50" s="8">
         <f t="shared" si="1"/>
-        <v>58575</v>
+        <v>118770</v>
       </c>
       <c r="D50" s="7"/>
     </row>
@@ -1164,9 +1164,9 @@
       <c r="B51" s="9">
         <v>5363</v>
       </c>
-      <c r="C51" s="8" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+      <c r="C51" s="8">
+        <f t="shared" si="1"/>
+        <v>124020</v>
       </c>
       <c r="D51" s="7"/>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="C52" s="8">
         <f t="shared" si="1"/>
-        <v>63825</v>
+        <v>129383</v>
       </c>
       <c r="D52" s="7"/>
     </row>
@@ -1190,9 +1190,9 @@
       <c r="B53" s="9">
         <v>5588</v>
       </c>
-      <c r="C53" s="8" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+      <c r="C53" s="8">
+        <f t="shared" si="1"/>
+        <v>134858</v>
       </c>
       <c r="D53" s="7"/>
     </row>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="C54" s="8">
         <f t="shared" si="1"/>
-        <v>69300</v>
+        <v>140446</v>
       </c>
       <c r="D54" s="7"/>
     </row>
@@ -1216,9 +1216,9 @@
       <c r="B55" s="9">
         <v>5813</v>
       </c>
-      <c r="C55" s="8" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+      <c r="C55" s="8">
+        <f t="shared" si="1"/>
+        <v>146146</v>
       </c>
       <c r="D55" s="7"/>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="C56" s="8">
         <f t="shared" si="1"/>
-        <v>75000</v>
+        <v>151959</v>
       </c>
       <c r="D56" s="7"/>
     </row>
@@ -1242,9 +1242,9 @@
       <c r="B57" s="9">
         <v>6038</v>
       </c>
-      <c r="C57" s="8" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+      <c r="C57" s="8">
+        <f t="shared" si="1"/>
+        <v>157884</v>
       </c>
       <c r="D57" s="7"/>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C58" s="8">
         <f t="shared" si="1"/>
-        <v>80925</v>
+        <v>163922</v>
       </c>
       <c r="D58" s="7"/>
     </row>
@@ -1268,9 +1268,9 @@
       <c r="B59" s="9">
         <v>6263</v>
       </c>
-      <c r="C59" s="8" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+      <c r="C59" s="8">
+        <f t="shared" si="1"/>
+        <v>170072</v>
       </c>
       <c r="D59" s="7"/>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C60" s="8">
         <f t="shared" si="1"/>
-        <v>87075</v>
+        <v>176335</v>
       </c>
       <c r="D60" s="7"/>
     </row>
@@ -1294,9 +1294,9 @@
       <c r="B61" s="9">
         <v>6488</v>
       </c>
-      <c r="C61" s="8" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+      <c r="C61" s="8">
+        <f t="shared" si="1"/>
+        <v>182710</v>
       </c>
       <c r="D61" s="7"/>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="C62" s="8">
         <f t="shared" si="1"/>
-        <v>93450</v>
+        <v>189198</v>
       </c>
       <c r="D62" s="7"/>
     </row>
@@ -1320,9 +1320,9 @@
       <c r="B63" s="9">
         <v>6713</v>
       </c>
-      <c r="C63" s="8" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+      <c r="C63" s="8">
+        <f t="shared" si="1"/>
+        <v>195798</v>
       </c>
       <c r="D63" s="7"/>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="C64" s="8">
         <f t="shared" si="1"/>
-        <v>100050</v>
+        <v>202511</v>
       </c>
       <c r="D64" s="7"/>
     </row>
@@ -1346,17 +1346,18 @@
       <c r="B65" s="9">
         <v>6938</v>
       </c>
-      <c r="C65" s="8" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
+      <c r="C65" s="8">
+        <f t="shared" si="1"/>
+        <v>209336</v>
       </c>
       <c r="D65" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>